--- a/examples/position-tags/关键岗位清单.xlsx
+++ b/examples/position-tags/关键岗位清单.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -71,10 +72,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,7 +446,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/examples/position-tags/关键岗位清单.xlsx
+++ b/examples/position-tags/关键岗位清单.xlsx
@@ -442,20 +442,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
+    <col width="10.8" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>配置类别</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -464,10 +470,15 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>关键岗位</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>J003</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>代表处一把手</t>
         </is>
@@ -476,10 +487,15 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>关键岗位</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>J006</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>核心研发岗</t>
         </is>
@@ -488,12 +504,34 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>关键岗位</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>J999</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>已撤销的岗位, 主表里没有 (清单里多出来的行不影响)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>保密岗位</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>J004</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>同一张清单里的另一类配置: 输入表的 筛选 只留 关键岗位 这一类, 所以 J004 不会被标成 关键岗位 (issue #30)</t>
         </is>
       </c>
     </row>
